--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0216.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0216.xlsx
@@ -11299,7 +11299,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Tìm đến khu vực ẩn "Rừng Bjartr"</t>
+          <t>Tìm đến khu vực ẩn "Bjartr Woods"</t>
         </is>
       </c>
     </row>
@@ -16369,7 +16369,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Mời 1 Cộng Hưởng Giả cùng đi Gondola.</t>
+          <t>Mời 1 Resonator cùng đi Gondola.</t>
         </is>
       </c>
     </row>
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Lần đầu đánh bại Fallacy of Không Return.</t>
+          <t>Lần đầu đánh bại Fallacy of No Return.</t>
         </is>
       </c>
     </row>
@@ -26119,7 +26119,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Đánh bại Fallacy of Không Return 50 lần.</t>
+          <t>Đánh bại Fallacy of No Return 50 lần.</t>
         </is>
       </c>
     </row>
@@ -28004,7 +28004,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Cộng Hưởng Giả bị hạ gục bởi đòn nổ của Zig Zags.</t>
+          <t>Resonator bị hạ gục bởi đòn nổ của Zig Zags.</t>
         </is>
       </c>
     </row>
@@ -28069,7 +28069,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Cộng Hưởng Giả bị hạ gục bởi đòn tấn công của Excarats.</t>
+          <t>Resonator bị hạ gục bởi đòn tấn công của Excarats.</t>
         </is>
       </c>
     </row>
@@ -28134,7 +28134,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Một Cộng Hưởng Giả bị hạ gục sau khi va chạm với Inferno Rider.</t>
+          <t>Một Resonator bị hạ gục sau khi va chạm với Inferno Rider.</t>
         </is>
       </c>
     </row>
@@ -28199,7 +28199,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Một Cộng Hưởng Giả bị hạ gục sau khi bị bọn Gulpuff tung hứng.</t>
+          <t>Một Resonator bị hạ gục sau khi bị bọn Gulpuff tung hứng.</t>
         </is>
       </c>
     </row>
@@ -28264,7 +28264,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Cộng Hưởng Giả bị hạ gục 10 lần do đòn tấn công bùng nổ của Hoartoise.</t>
+          <t>Resonator bị hạ gục 10 lần do đòn tấn công bùng nổ của Hoartoise.</t>
         </is>
       </c>
     </row>
@@ -28654,7 +28654,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Bản Hologram Chiến Thuật Hoàn Chỉnh: Thảm Họa - Bão Mephis I.</t>
+          <t>Bản Hologram Chiến Thuật Hoàn Chỉnh: Calamity - Tempest Mephis I.</t>
         </is>
       </c>
     </row>
@@ -28719,7 +28719,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Hoàn thành Bản Hologram Chiến Thuật: Đại Họa - Impermanence Heron I</t>
+          <t>Hoàn thành Bản Hologram Chiến Thuật: Calamity - Impermanence Heron I.</t>
         </is>
       </c>
     </row>
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Hoàn thành Bản Hologram Chiến Thuật: Đại Họa - Mourning Aix I</t>
+          <t>Hoàn thành Bản Hologram Chiến Thuật: Calamity - Mourning Aix I.</t>
         </is>
       </c>
     </row>
@@ -28849,7 +28849,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Hoàn thành Bản Hologram Chiến Thuật: Đại Họa - Feilian Beringal I</t>
+          <t>Hoàn thành Bản Hologram Chiến Thuật: Calamity - Feilian Beringal I.</t>
         </is>
       </c>
     </row>
@@ -28979,7 +28979,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Bản Hologram Chiến Thuật Hoàn Chỉnh: Thảm Họa - Bão Mephis VI.</t>
+          <t>Bản Hologram Chiến Thuật Hoàn Chỉnh: Calamity - Tempest Mephis VI.</t>
         </is>
       </c>
     </row>
@@ -29044,7 +29044,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Hoàn thành Bản Hologram Chiến Thuật: Đại Họa - Impermanence Heron VI</t>
+          <t>Hoàn thành Bản Hologram Chiến Thuật: Calamity - Impermanence Heron VI.</t>
         </is>
       </c>
     </row>
@@ -29109,7 +29109,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Hoàn thành Bản Hologram Chiến Thuật: Đại Họa - Mourning Aix VI</t>
+          <t>Hoàn thành Bản Hologram Chiến Thuật: Calamity - Mourning Aix VI.</t>
         </is>
       </c>
     </row>
@@ -29174,7 +29174,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Hoàn thành Bản Hologram Chiến Thuật: Đại Họa - Feilian Beringal VI</t>
+          <t>Hoàn thành Bản Hologram Chiến Thuật: Calamity - Feilian Beringal VI.</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Hoàn thành Hologram Chiến Thuật: Tai Họa - Vô Đỉnh I.</t>
+          <t>Hoàn thành Hologram Chiến Thuật: Calamity - Crownless I.</t>
         </is>
       </c>
     </row>
@@ -29499,7 +29499,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Hoàn thành Bản Hologram Chiến Thuật: Đại Họa - Crownless VI</t>
+          <t>Hoàn thành Bản Hologram Chiến Thuật: Calamity - Crownless VI.</t>
         </is>
       </c>
     </row>
@@ -29564,7 +29564,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Hoàn thành Bản Hologram Chiến Thuật: Đại Họa - Inferno Rider I</t>
+          <t>Hoàn thành Bản Hologram Chiến Thuật: Calamity - Inferno Rider I.</t>
         </is>
       </c>
     </row>
@@ -29629,7 +29629,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Hoàn thành Bản Hologram Chiến Thuật: Đại Họa - Inferno Rider VI</t>
+          <t>Hoàn thành Bản Hologram Chiến Thuật: Calamity - Inferno Rider VI.</t>
         </is>
       </c>
     </row>
@@ -31711,7 +31711,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Một Cộng Hưởng Giả bị hạ gục bởi đòn tấn công của Sigillum.</t>
+          <t>Một Resonator bị hạ gục bởi đòn tấn công của Sigillum.</t>
         </is>
       </c>
     </row>
@@ -31776,7 +31776,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Một Cộng Hưởng Giả bị hạ gục bởi đòn tấn công của Nameless Explorer.</t>
+          <t>Một Resonator bị hạ gục bởi đòn tấn công của Nameless Explorer.</t>
         </is>
       </c>
     </row>
@@ -31841,7 +31841,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Một Cộng Hưởng Giả bị hạ gục bởi đòn tấn công của Kronablight.</t>
+          <t>Một Resonator bị hạ gục bởi đòn tấn công của Kronablight.</t>
         </is>
       </c>
     </row>
@@ -31906,7 +31906,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Một Cộng Hưởng Giả bị hạ gục bởi đòn tấn công của Kronaclaw.</t>
+          <t>Một Resonator bị hạ gục bởi đòn tấn công của Kronaclaw.</t>
         </is>
       </c>
     </row>
@@ -31971,7 +31971,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Một Cộng Hưởng Giả bị hạ gục bởi đòn tấn công của Glommoth.</t>
+          <t>Một Resonator bị hạ gục bởi đòn tấn công của Glommoth.</t>
         </is>
       </c>
     </row>
@@ -32036,7 +32036,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Một Cộng Hưởng Giả bị hạ gục bởi đòn tấn công của Iceglint Dancer.</t>
+          <t>Một Resonator bị hạ gục bởi đòn tấn công của Iceglint Dancer.</t>
         </is>
       </c>
     </row>
@@ -32101,7 +32101,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Một Cộng Hưởng Giả bị hạ gục bởi đòn tấn công của Shadow Stepper.</t>
+          <t>Một Resonator bị hạ gục bởi đòn tấn công của Shadow Stepper.</t>
         </is>
       </c>
     </row>
@@ -32166,7 +32166,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Cộng Hưởng Giả đã đạt Cấp 6.</t>
+          <t>Resonator đã đạt Cấp 6.</t>
         </is>
       </c>
     </row>
@@ -32426,7 +32426,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Tuyển mộ tổng cộng 3 Cộng Hưởng Giả.</t>
+          <t>Tuyển mộ tổng cộng 3 Resonator.</t>
         </is>
       </c>
     </row>
@@ -32491,7 +32491,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Thu thập tổng cộng 6 Cộng Hưởng Giả.</t>
+          <t>Thu thập tổng cộng 6 Resonator.</t>
         </is>
       </c>
     </row>
@@ -32556,7 +32556,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Thu thập tổng cộng 10 Cộng Hưởng Giả</t>
+          <t>Thu thập tổng cộng 10 Resonator</t>
         </is>
       </c>
     </row>
@@ -33011,7 +33011,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Nâng cấp tất cả kỹ năng của bất kỳ Cộng Hưởng Giả nào lên cấp tối đa.</t>
+          <t>Nâng cấp tất cả kỹ năng của bất kỳ Resonator nào lên cấp tối đa.</t>
         </is>
       </c>
     </row>
